--- a/PSCBOX_YANGPYEONG_S18.xlsx
+++ b/PSCBOX_YANGPYEONG_S18.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N191"/>
+  <dimension ref="A1:N194"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3061,53 +3061,74 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>srebar</t>
-        </is>
-      </c>
-      <c r="B190" t="inlineStr">
-        <is>
-          <t>T4-1</t>
-        </is>
-      </c>
-      <c r="C190" t="n">
-        <v>21</v>
-      </c>
-      <c r="D190" t="n">
-        <v>13</v>
-      </c>
-      <c r="E190" t="inlineStr">
-        <is>
-          <t>2000,-7920,90</t>
-        </is>
-      </c>
-      <c r="F190" t="inlineStr">
-        <is>
-          <t>-1000,1000</t>
-        </is>
-      </c>
-      <c r="G190" t="n">
-        <v>3</v>
-      </c>
-      <c r="H190" t="n">
-        <v>1000</v>
-      </c>
-      <c r="I190" t="n">
-        <v>150</v>
-      </c>
-      <c r="J190" t="inlineStr"/>
-      <c r="K190" t="inlineStr"/>
-      <c r="L190" t="inlineStr"/>
-      <c r="M190" t="n">
-        <v>3</v>
-      </c>
-      <c r="N190" t="inlineStr">
-        <is>
-          <t>bottom slab tie, right  (2-070 T4 H13)</t>
+          <t>#         오른쪽은 **거울로** 돌린다 (rot -90 · 다리가 +x). 처음에 왼쪽과 같은 90 으로 두었더니</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
+        <is>
+          <t>#         오른쪽 헌치에서 위 다리가 **내리막**으로 누워 x 3,000 의 ㄷ 가 300 mm 비스듬히 섰다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>#         복부 T3 / T3-1 (193 / 167) 은 거울로 두었으면서 여기만 빠뜨렸던 것이다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>srebar</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>T4-1</t>
+        </is>
+      </c>
+      <c r="C193" t="n">
+        <v>21</v>
+      </c>
+      <c r="D193" t="n">
+        <v>13</v>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>2000,-7920,-90</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>-1000,1000</t>
+        </is>
+      </c>
+      <c r="G193" t="n">
+        <v>3</v>
+      </c>
+      <c r="H193" t="n">
+        <v>1000</v>
+      </c>
+      <c r="I193" t="n">
+        <v>150</v>
+      </c>
+      <c r="J193" t="inlineStr"/>
+      <c r="K193" t="inlineStr"/>
+      <c r="L193" t="inlineStr"/>
+      <c r="M193" t="n">
+        <v>3</v>
+      </c>
+      <c r="N193" t="inlineStr">
+        <is>
+          <t>bottom slab tie, right  (2-070 T4 H13)</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
         <is>
           <t>end</t>
         </is>

--- a/PSCBOX_YANGPYEONG_S18.xlsx
+++ b/PSCBOX_YANGPYEONG_S18.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N194"/>
+  <dimension ref="A1:N196"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3082,53 +3082,67 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>srebar</t>
-        </is>
-      </c>
-      <c r="B193" t="inlineStr">
-        <is>
-          <t>T4-1</t>
-        </is>
-      </c>
-      <c r="C193" t="n">
-        <v>21</v>
-      </c>
-      <c r="D193" t="n">
-        <v>13</v>
-      </c>
-      <c r="E193" t="inlineStr">
-        <is>
-          <t>2000,-7920,-90</t>
-        </is>
-      </c>
-      <c r="F193" t="inlineStr">
-        <is>
-          <t>-1000,1000</t>
-        </is>
-      </c>
-      <c r="G193" t="n">
-        <v>3</v>
-      </c>
-      <c r="H193" t="n">
-        <v>1000</v>
-      </c>
-      <c r="I193" t="n">
-        <v>150</v>
-      </c>
-      <c r="J193" t="inlineStr"/>
-      <c r="K193" t="inlineStr"/>
-      <c r="L193" t="inlineStr"/>
-      <c r="M193" t="n">
-        <v>3</v>
-      </c>
-      <c r="N193" t="inlineStr">
-        <is>
-          <t>bottom slab tie, right  (2-070 T4 H13)</t>
+          <t>#         2026-10-14 : 까닭은 엔진이었다 — ㄷ 의 **몸통**이 옆 복부 외측면과 나란해지려 돌았다.</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
+        <is>
+          <t>#         고친 뒤로는 90 이어도 곧게 선다. 좌우 대칭이라 거울로 둔다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>srebar</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>T4-1</t>
+        </is>
+      </c>
+      <c r="C195" t="n">
+        <v>21</v>
+      </c>
+      <c r="D195" t="n">
+        <v>13</v>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>2000,-7920,-90</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>-1000,1000</t>
+        </is>
+      </c>
+      <c r="G195" t="n">
+        <v>3</v>
+      </c>
+      <c r="H195" t="n">
+        <v>1000</v>
+      </c>
+      <c r="I195" t="n">
+        <v>150</v>
+      </c>
+      <c r="J195" t="inlineStr"/>
+      <c r="K195" t="inlineStr"/>
+      <c r="L195" t="inlineStr"/>
+      <c r="M195" t="n">
+        <v>3</v>
+      </c>
+      <c r="N195" t="inlineStr">
+        <is>
+          <t>bottom slab tie, right  (2-070 T4 H13)</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
         <is>
           <t>end</t>
         </is>

--- a/PSCBOX_YANGPYEONG_S18.xlsx
+++ b/PSCBOX_YANGPYEONG_S18.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N196"/>
+  <dimension ref="A1:N200"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2834,262 +2834,98 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>#  T1 T2  상부슬래브 : C-C 에 세로 토막 47 개가 @500 (−11,728 ~ +11,723, 복부 자리만 빈다)</t>
+          <t>#  T1 T2  상부슬래브 : C-C 의 세로 토막이 −11,728 ~ +11,723 @500 — **48 자리**다 (복부 위는 엔진이 버린다)</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>#         2-070 은 캔틸레버 쪽을 T1, 헌치 쪽을 T2 로 부른다 — 꼴이 같아 한 줄로 넣는다</t>
+          <t>#         처음에 47 로 넣었다(도면의 선 47 개를 셌는데 겹친 선 둘 · 복부 자리 빈 것이 섞여 있었다).</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>#  T3     복부 : 면마다 15 개 @500 (깊이 -885 ~ -7,885)</t>
+          <t>#         그러면 같은 ±11,750 에 47 개가 서서 열차가 **반 칸(250) 어긋났다** — 도면 비교표에서 드러났다.</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>#  T4     하부슬래브 전깊이 : ±1,000 · ±2,000 · ±3,000 (C-C 는 ±1,029 ±2,033 ±3,031, **가운데 없음**)</t>
+          <t>#         몸통은 상면 점의 26 mm 오른쪽 · 다리는 −x (도면 그대로)</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>#         가운데를 비우려고 왼쪽 · 오른쪽 두 줄로 넣는다 (한 줄 @1,000 이면 0 에 하나가 선다)</t>
+          <t>#         2-070 은 캔틸레버 쪽을 T1, 헌치 쪽을 T2 로 부른다 — 꼴이 같아 한 줄로 넣는다</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>srebar</t>
-        </is>
-      </c>
-      <c r="B186" t="inlineStr">
-        <is>
-          <t>T1</t>
-        </is>
-      </c>
-      <c r="C186" t="n">
-        <v>21</v>
-      </c>
-      <c r="D186" t="n">
-        <v>13</v>
-      </c>
-      <c r="E186" t="inlineStr">
-        <is>
-          <t>0,-170,90</t>
-        </is>
-      </c>
-      <c r="F186" t="inlineStr">
-        <is>
-          <t>-11750,11750</t>
-        </is>
-      </c>
-      <c r="G186" t="n">
-        <v>47</v>
-      </c>
-      <c r="H186" t="n">
-        <v>500</v>
-      </c>
-      <c r="I186" t="n">
-        <v>150</v>
-      </c>
-      <c r="J186" t="inlineStr"/>
-      <c r="K186" t="inlineStr"/>
-      <c r="L186" t="inlineStr"/>
-      <c r="M186" t="n">
-        <v>1</v>
-      </c>
-      <c r="N186" t="inlineStr">
-        <is>
-          <t>top slab tie  (2-070 T1 T2 H13)</t>
+          <t>#  T3     복부 : 면마다 15 개. ! 도면은 **수평** 토막을 **세로 500** 간격으로 그린다 (y −1,382 ~ −6,882).</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>srebar</t>
-        </is>
-      </c>
-      <c r="B187" t="inlineStr">
-        <is>
-          <t>T3</t>
-        </is>
-      </c>
-      <c r="C187" t="n">
-        <v>21</v>
-      </c>
-      <c r="D187" t="n">
-        <v>13</v>
-      </c>
-      <c r="E187" t="inlineStr">
-        <is>
-          <t>-4808,-4320,193</t>
-        </is>
-      </c>
-      <c r="F187" t="inlineStr">
-        <is>
-          <t>-4200,4200</t>
-        </is>
-      </c>
-      <c r="G187" t="n">
-        <v>15</v>
-      </c>
-      <c r="H187" t="n">
-        <v>500</v>
-      </c>
-      <c r="I187" t="n">
-        <v>150</v>
-      </c>
-      <c r="J187" t="inlineStr"/>
-      <c r="K187" t="inlineStr"/>
-      <c r="L187" t="inlineStr"/>
-      <c r="M187" t="n">
-        <v>2</v>
-      </c>
-      <c r="N187" t="inlineStr">
-        <is>
-          <t>left  web tie  (2-070 T3 H13)</t>
+          <t>#         시트 문법은 타이 열차가 몸통에 수직으로 달리므로 «경사 복부를 따라 수평 몸통»을 못 적는다 —</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>srebar</t>
-        </is>
-      </c>
-      <c r="B188" t="inlineStr">
-        <is>
-          <t>T3-1</t>
-        </is>
-      </c>
-      <c r="C188" t="n">
-        <v>21</v>
-      </c>
-      <c r="D188" t="n">
-        <v>13</v>
-      </c>
-      <c r="E188" t="inlineStr">
-        <is>
-          <t>4808,-4320,167</t>
-        </is>
-      </c>
-      <c r="F188" t="inlineStr">
-        <is>
-          <t>-4200,4200</t>
-        </is>
-      </c>
-      <c r="G188" t="n">
-        <v>15</v>
-      </c>
-      <c r="H188" t="n">
-        <v>500</v>
-      </c>
-      <c r="I188" t="n">
-        <v>150</v>
-      </c>
-      <c r="J188" t="inlineStr"/>
-      <c r="K188" t="inlineStr"/>
-      <c r="L188" t="inlineStr"/>
-      <c r="M188" t="n">
-        <v>2</v>
-      </c>
-      <c r="N188" t="inlineStr">
-        <is>
-          <t>right web tie  (2-070 T3 H13)</t>
+          <t>#         복부에 수직(193 / 167)으로 둔다. 비교표의 모형 한계 칸에 있다.</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>srebar</t>
-        </is>
-      </c>
-      <c r="B189" t="inlineStr">
-        <is>
-          <t>T4</t>
-        </is>
-      </c>
-      <c r="C189" t="n">
-        <v>21</v>
-      </c>
-      <c r="D189" t="n">
-        <v>13</v>
-      </c>
-      <c r="E189" t="inlineStr">
-        <is>
-          <t>-2000,-7920,90</t>
-        </is>
-      </c>
-      <c r="F189" t="inlineStr">
-        <is>
-          <t>-1000,1000</t>
-        </is>
-      </c>
-      <c r="G189" t="n">
-        <v>3</v>
-      </c>
-      <c r="H189" t="n">
-        <v>1000</v>
-      </c>
-      <c r="I189" t="n">
-        <v>150</v>
-      </c>
-      <c r="J189" t="inlineStr"/>
-      <c r="K189" t="inlineStr"/>
-      <c r="L189" t="inlineStr"/>
-      <c r="M189" t="n">
-        <v>3</v>
-      </c>
-      <c r="N189" t="inlineStr">
-        <is>
-          <t>bottom slab tie, left   (2-070 T4 H13)</t>
+          <t>#  T4     하부슬래브 전깊이 : C-C 는 ±1,029 ±2,033 ±3,031, **가운데 없음**</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>#         오른쪽은 **거울로** 돌린다 (rot -90 · 다리가 +x). 처음에 왼쪽과 같은 90 으로 두었더니</t>
+          <t>#         몸통이 점의 **바깥쪽**(|x| 큰 쪽)에 서고 다리는 **중심선 쪽**으로 뻗는다 (−1,029 몸통 · −1,000 점).</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>#         오른쪽 헌치에서 위 다리가 **내리막**으로 누워 x 3,000 의 ㄷ 가 300 mm 비스듬히 섰다.</t>
+          <t>#         10-13 에 오른쪽을 거울로 돌리며 다리를 바깥(+x)으로 두었는데 도면과 **양쪽 다 반대**였다 — 비교표에서</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>#         복부 T3 / T3-1 (193 / 167) 은 거울로 두었으면서 여기만 빠뜨렸던 것이다.</t>
+          <t>#         62~73 mm 어긋남으로 드러났다. 왼쪽 rot −90 (다리 +x) · 오른쪽 rot 90 (다리 −x).</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>#         2026-10-14 : 까닭은 엔진이었다 — ㄷ 의 **몸통**이 옆 복부 외측면과 나란해지려 돌았다.</t>
+          <t>#         (10-14 엔진 수정 뒤로는 어느 쪽으로 넣어도 곧게 선다 — 방향은 도면이 정한다.)</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>#         고친 뒤로는 90 이어도 곧게 선다. 좌우 대칭이라 거울로 둔다.</t>
+          <t>#         가운데를 비우려고 왼쪽 · 오른쪽 두 줄로 넣는다 (한 줄 @1,000 이면 0 에 하나가 선다)</t>
         </is>
       </c>
     </row>
@@ -3101,7 +2937,7 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>T4-1</t>
+          <t>T1</t>
         </is>
       </c>
       <c r="C195" t="n">
@@ -3112,19 +2948,19 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>2000,-7920,-90</t>
+          <t>0,-170,90</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>-1000,1000</t>
+          <t>-11750,11750</t>
         </is>
       </c>
       <c r="G195" t="n">
-        <v>3</v>
+        <v>48</v>
       </c>
       <c r="H195" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="I195" t="n">
         <v>150</v>
@@ -3133,16 +2969,208 @@
       <c r="K195" t="inlineStr"/>
       <c r="L195" t="inlineStr"/>
       <c r="M195" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N195" t="inlineStr">
         <is>
-          <t>bottom slab tie, right  (2-070 T4 H13)</t>
+          <t>top slab tie  (2-070 T1 T2 H13)</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
+        <is>
+          <t>srebar</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>T3</t>
+        </is>
+      </c>
+      <c r="C196" t="n">
+        <v>21</v>
+      </c>
+      <c r="D196" t="n">
+        <v>13</v>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>-4808,-4320,193</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>-4200,4200</t>
+        </is>
+      </c>
+      <c r="G196" t="n">
+        <v>15</v>
+      </c>
+      <c r="H196" t="n">
+        <v>500</v>
+      </c>
+      <c r="I196" t="n">
+        <v>150</v>
+      </c>
+      <c r="J196" t="inlineStr"/>
+      <c r="K196" t="inlineStr"/>
+      <c r="L196" t="inlineStr"/>
+      <c r="M196" t="n">
+        <v>2</v>
+      </c>
+      <c r="N196" t="inlineStr">
+        <is>
+          <t>left  web tie  (2-070 T3 H13)</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>srebar</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>T3-1</t>
+        </is>
+      </c>
+      <c r="C197" t="n">
+        <v>21</v>
+      </c>
+      <c r="D197" t="n">
+        <v>13</v>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>4808,-4320,167</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>-4200,4200</t>
+        </is>
+      </c>
+      <c r="G197" t="n">
+        <v>15</v>
+      </c>
+      <c r="H197" t="n">
+        <v>500</v>
+      </c>
+      <c r="I197" t="n">
+        <v>150</v>
+      </c>
+      <c r="J197" t="inlineStr"/>
+      <c r="K197" t="inlineStr"/>
+      <c r="L197" t="inlineStr"/>
+      <c r="M197" t="n">
+        <v>2</v>
+      </c>
+      <c r="N197" t="inlineStr">
+        <is>
+          <t>right web tie  (2-070 T3 H13)</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>srebar</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
+      <c r="C198" t="n">
+        <v>21</v>
+      </c>
+      <c r="D198" t="n">
+        <v>13</v>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>-2000,-7920,-90</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>-1000,1000</t>
+        </is>
+      </c>
+      <c r="G198" t="n">
+        <v>3</v>
+      </c>
+      <c r="H198" t="n">
+        <v>1000</v>
+      </c>
+      <c r="I198" t="n">
+        <v>150</v>
+      </c>
+      <c r="J198" t="inlineStr"/>
+      <c r="K198" t="inlineStr"/>
+      <c r="L198" t="inlineStr"/>
+      <c r="M198" t="n">
+        <v>3</v>
+      </c>
+      <c r="N198" t="inlineStr">
+        <is>
+          <t>bottom slab tie, left   (2-070 T4 H13)</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>srebar</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>T4-1</t>
+        </is>
+      </c>
+      <c r="C199" t="n">
+        <v>21</v>
+      </c>
+      <c r="D199" t="n">
+        <v>13</v>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>2000,-7920,90</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>-1000,1000</t>
+        </is>
+      </c>
+      <c r="G199" t="n">
+        <v>3</v>
+      </c>
+      <c r="H199" t="n">
+        <v>1000</v>
+      </c>
+      <c r="I199" t="n">
+        <v>150</v>
+      </c>
+      <c r="J199" t="inlineStr"/>
+      <c r="K199" t="inlineStr"/>
+      <c r="L199" t="inlineStr"/>
+      <c r="M199" t="n">
+        <v>3</v>
+      </c>
+      <c r="N199" t="inlineStr">
+        <is>
+          <t>bottom slab tie, right  (2-070 T4 H13)</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
         <is>
           <t>end</t>
         </is>
